--- a/ExcelTool/LubanTools/DataTables/Datas/NpcSpawnGroupData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/NpcSpawnGroupData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{165A946B-3646-45F1-BBC5-6C0FB44791DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7060F4DB-7E9C-4966-A909-050CEB75C7B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="58965" yWindow="11490" windowWidth="42465" windowHeight="19845" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11290" yWindow="5550" windowWidth="38610" windowHeight="19220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -569,7 +569,7 @@
         <v>15</v>
       </c>
       <c r="E4" s="1">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>22</v>
